--- a/बजेट माग estimate/devithaan baaje/devithaan.xlsx
+++ b/बजेट माग estimate/devithaan baaje/devithaan.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592DDA3B-41CE-45EC-8753-0F0776C8FD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11040"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="estimate" sheetId="12" r:id="rId1"/>
@@ -36,10 +37,10 @@
     <definedName name="description_781">#REF!</definedName>
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$70</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="56">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -217,15 +218,21 @@
   </si>
   <si>
     <t>Project:-देविथान निर्माण कार्य</t>
+  </si>
+  <si>
+    <t>- for open space</t>
+  </si>
+  <si>
+    <t>-diagonal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -399,13 +406,13 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -413,7 +420,7 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -437,14 +444,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -463,7 +470,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -478,7 +485,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -495,23 +502,35 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -532,60 +551,35 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="3"/>
+    <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 3" xfId="5"/>
-    <cellStyle name="Percent 2" xfId="4"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Percent 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -601,7 +595,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -695,7 +689,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -754,7 +748,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -818,9 +812,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -858,9 +852,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -895,7 +889,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -930,7 +924,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1103,135 +1097,135 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S65"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S70"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="19" customWidth="1"/>
-    <col min="2" max="2" width="30.88671875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" style="19" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" style="19" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" style="19"/>
+    <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="19" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="19" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="19"/>
     <col min="8" max="8" width="5" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.109375" style="19"/>
+    <col min="9" max="9" width="9.5703125" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.140625" style="19"/>
     <col min="13" max="16" width="0" style="19" hidden="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.109375" style="19"/>
+    <col min="17" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-    </row>
-    <row r="2" spans="1:16" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+    </row>
+    <row r="2" spans="1:16" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="41" t="s">
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-    </row>
-    <row r="5" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="42" t="s">
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+    </row>
+    <row r="5" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-    </row>
-    <row r="6" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="37" t="s">
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
+    </row>
+    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="38" t="s">
+      <c r="H6" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-    </row>
-    <row r="7" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="45" t="s">
+      <c r="I6" s="55"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
+    </row>
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="46" t="s">
+      <c r="H7" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-    </row>
-    <row r="8" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
+    </row>
+    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>6</v>
       </c>
@@ -1266,7 +1260,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="188.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="188.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>1</v>
       </c>
@@ -1283,7 +1277,7 @@
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="32" t="s">
         <v>30</v>
@@ -1323,15 +1317,15 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="32"/>
       <c r="C11" s="17">
         <v>1</v>
       </c>
       <c r="D11" s="33">
-        <f>5.5+2</f>
-        <v>7.5</v>
+        <f>5.5+2.4</f>
+        <v>7.9</v>
       </c>
       <c r="E11" s="33">
         <f>F11/2</f>
@@ -1342,18 +1336,18 @@
       </c>
       <c r="G11" s="33">
         <f>PRODUCT(C11:F11)</f>
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
-      <c r="M11" s="50"/>
-      <c r="N11" s="50"/>
-      <c r="O11" s="50"/>
-      <c r="P11" s="50"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="32"/>
       <c r="C12" s="17">
@@ -1377,73 +1371,106 @@
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
-      <c r="M12" s="50"/>
-      <c r="N12" s="50"/>
-      <c r="O12" s="50"/>
-      <c r="P12" s="50"/>
-    </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="6">
-        <f>SUM(G10:G12)</f>
-        <v>95.64</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" s="6">
-        <v>62.95</v>
-      </c>
-      <c r="J13" s="18">
-        <f>G13*I13</f>
-        <v>6020.5380000000005</v>
-      </c>
-      <c r="K13" s="5"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="16"/>
+      <c r="B13" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="17">
+        <f>4*2</f>
+        <v>8</v>
+      </c>
+      <c r="D13" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="E13" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="F13" s="33">
+        <v>0.6</v>
+      </c>
+      <c r="G13" s="33">
+        <f>PRODUCT(C13:F13)</f>
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
-      <c r="B14" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
+      <c r="B14" s="32" t="str">
+        <f>B23</f>
+        <v>- for open space</v>
+      </c>
+      <c r="C14" s="17">
+        <f>C23</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="33">
+        <f>D23</f>
+        <v>10</v>
+      </c>
+      <c r="E14" s="33">
+        <f t="shared" ref="E14:F14" si="0">E23</f>
+        <v>1.2</v>
+      </c>
+      <c r="F14" s="33">
+        <f t="shared" si="0"/>
+        <v>0.15</v>
+      </c>
+      <c r="G14" s="33">
+        <f>PRODUCT(C14:F14)</f>
+        <v>1.7999999999999998</v>
+      </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
-      <c r="J14" s="18">
-        <f>0.13*G13*(18612)/360</f>
-        <v>642.79644000000008</v>
-      </c>
+      <c r="J14" s="17"/>
       <c r="K14" s="17"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="16"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-    </row>
-    <row r="16" spans="1:16" ht="109.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="16">
-        <v>2</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>31</v>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+    </row>
+    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="6">
+        <f>SUM(G10:G14)</f>
+        <v>99.211999999999989</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="6">
+        <v>62.95</v>
+      </c>
+      <c r="J15" s="18">
+        <f>G15*I15</f>
+        <v>6245.3953999999994</v>
+      </c>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="16"/>
+      <c r="B16" s="32" t="s">
+        <v>24</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
@@ -1452,365 +1479,343 @@
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
+      <c r="J16" s="18">
+        <f>0.13*G15*(18612)/360</f>
+        <v>666.80385199999989</v>
+      </c>
       <c r="K16" s="17"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
-      <c r="B17" s="32" t="str">
-        <f>B10</f>
-        <v>-for masonary wall</v>
-      </c>
-      <c r="C17" s="17">
-        <v>1</v>
-      </c>
-      <c r="D17" s="33">
-        <f>D10</f>
-        <v>17.5</v>
-      </c>
-      <c r="E17" s="33">
-        <f>E10</f>
-        <v>1.5</v>
-      </c>
-      <c r="F17" s="33">
-        <v>0.15</v>
-      </c>
-      <c r="G17" s="33">
-        <f>PRODUCT(C17:F17)</f>
-        <v>3.9375</v>
-      </c>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
-      <c r="M17" s="33">
-        <f>7</f>
-        <v>7</v>
-      </c>
-      <c r="N17" s="33">
-        <f>2</f>
+    </row>
+    <row r="18" spans="1:16" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="16">
         <v>2</v>
       </c>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33">
-        <f>PI()*M17*SQRT(M17^2+N17^2)</f>
-        <v>160.09797821843054</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="16"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="17">
-        <v>1</v>
-      </c>
-      <c r="D18" s="33">
-        <f>D11</f>
-        <v>7.5</v>
-      </c>
-      <c r="E18" s="33">
-        <f>E11</f>
-        <v>1</v>
-      </c>
-      <c r="F18" s="33">
-        <v>0.15</v>
-      </c>
-      <c r="G18" s="33">
-        <f>PRODUCT(C18:F18)</f>
-        <v>1.125</v>
-      </c>
+      <c r="B18" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
       <c r="K18" s="17"/>
-      <c r="M18" s="50"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="50"/>
-      <c r="P18" s="50"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
-      <c r="B19" s="32"/>
+      <c r="B19" s="32" t="str">
+        <f>B10</f>
+        <v>-for masonary wall</v>
+      </c>
       <c r="C19" s="17">
         <v>1</v>
       </c>
       <c r="D19" s="33">
-        <f>D12</f>
-        <v>10.5</v>
+        <f>D10</f>
+        <v>17.5</v>
       </c>
       <c r="E19" s="33">
-        <f>E12</f>
-        <v>1.2</v>
+        <f>E10</f>
+        <v>1.5</v>
       </c>
       <c r="F19" s="33">
         <v>0.15</v>
       </c>
       <c r="G19" s="33">
         <f>PRODUCT(C19:F19)</f>
-        <v>1.89</v>
+        <v>3.9375</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
       <c r="J19" s="17"/>
       <c r="K19" s="17"/>
-      <c r="M19" s="50"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="50"/>
-      <c r="P19" s="50"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M19" s="33">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="N19" s="33">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="O19" s="33"/>
+      <c r="P19" s="33">
+        <f>PI()*M19*SQRT(M19^2+N19^2)</f>
+        <v>160.09797821843054</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
-      <c r="B20" s="32" t="s">
-        <v>52</v>
-      </c>
+      <c r="B20" s="32"/>
       <c r="C20" s="17">
-        <f>4*2</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D20" s="33">
-        <v>0.45</v>
+        <f>D11</f>
+        <v>7.9</v>
       </c>
       <c r="E20" s="33">
-        <v>0.45</v>
+        <f>E11</f>
+        <v>1</v>
       </c>
       <c r="F20" s="33">
         <v>0.15</v>
       </c>
       <c r="G20" s="33">
         <f>PRODUCT(C20:F20)</f>
-        <v>0.24299999999999999</v>
+        <v>1.1850000000000001</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
       <c r="K20" s="17"/>
-      <c r="M20" s="50"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="50"/>
-      <c r="P20" s="50"/>
-    </row>
-    <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="6">
-        <f>SUM(G17:G20)</f>
-        <v>7.1955</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I21" s="6">
-        <v>4458.5200000000004</v>
-      </c>
-      <c r="J21" s="18">
-        <f>G21*I21</f>
-        <v>32081.280660000004</v>
-      </c>
-      <c r="K21" s="5"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="16"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="17">
+        <v>1</v>
+      </c>
+      <c r="D21" s="33">
+        <f>D12</f>
+        <v>10.5</v>
+      </c>
+      <c r="E21" s="33">
+        <f>E12</f>
+        <v>1.2</v>
+      </c>
+      <c r="F21" s="33">
+        <v>0.15</v>
+      </c>
+      <c r="G21" s="33">
+        <f>PRODUCT(C21:F21)</f>
+        <v>1.89</v>
+      </c>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
+        <v>52</v>
+      </c>
+      <c r="C22" s="17">
+        <f>4*2</f>
+        <v>8</v>
+      </c>
+      <c r="D22" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="E22" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="F22" s="33">
+        <v>0.15</v>
+      </c>
+      <c r="G22" s="33">
+        <f>PRODUCT(C22:F22)</f>
+        <v>0.24299999999999999</v>
+      </c>
       <c r="H22" s="17"/>
       <c r="I22" s="17"/>
-      <c r="J22" s="18">
-        <f>0.13*G21*(14817.6)/5</f>
-        <v>2772.1210608000001</v>
-      </c>
+      <c r="J22" s="17"/>
       <c r="K22" s="17"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
+      <c r="B23" s="32" t="str">
+        <f>B35</f>
+        <v>- for open space</v>
+      </c>
+      <c r="C23" s="17">
+        <f>C35</f>
+        <v>1</v>
+      </c>
+      <c r="D23" s="33">
+        <f>D35</f>
+        <v>10</v>
+      </c>
+      <c r="E23" s="33">
+        <f>E35</f>
+        <v>1.2</v>
+      </c>
+      <c r="F23" s="33">
+        <v>0.15</v>
+      </c>
+      <c r="G23" s="33">
+        <f>PRODUCT(C23:F23)</f>
+        <v>1.7999999999999998</v>
+      </c>
       <c r="H23" s="17"/>
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
-    </row>
-    <row r="24" spans="1:16" ht="78" x14ac:dyDescent="0.3">
-      <c r="A24" s="16">
-        <v>3</v>
-      </c>
-      <c r="B24" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M23" s="36"/>
+      <c r="N23" s="36"/>
+      <c r="O23" s="36"/>
+      <c r="P23" s="36"/>
+    </row>
+    <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="6">
+        <f>SUM(G19:G23)</f>
+        <v>9.0555000000000003</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="6">
+        <v>4458.5200000000004</v>
+      </c>
+      <c r="J24" s="18">
+        <f>G24*I24</f>
+        <v>40374.127860000008</v>
+      </c>
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
-      <c r="B25" s="32" t="str">
-        <f>B17</f>
-        <v>-for masonary wall</v>
-      </c>
-      <c r="C25" s="17">
-        <v>1</v>
-      </c>
-      <c r="D25" s="33">
-        <f>D17</f>
-        <v>17.5</v>
-      </c>
-      <c r="E25" s="33">
-        <f>E17</f>
-        <v>1.5</v>
-      </c>
-      <c r="F25" s="33">
-        <v>0.05</v>
-      </c>
-      <c r="G25" s="33">
-        <f>PRODUCT(C25:F25)</f>
-        <v>1.3125</v>
-      </c>
+      <c r="B25" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
       <c r="H25" s="17"/>
       <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
+      <c r="J25" s="18">
+        <f>0.13*G24*(14817.6)/5</f>
+        <v>3488.7001968000004</v>
+      </c>
       <c r="K25" s="17"/>
-      <c r="M25" s="33">
-        <f>7</f>
-        <v>7</v>
-      </c>
-      <c r="N25" s="33">
-        <f>2</f>
-        <v>2</v>
-      </c>
-      <c r="O25" s="33"/>
-      <c r="P25" s="33">
-        <f>PI()*M25*SQRT(M25^2+N25^2)</f>
-        <v>160.09797821843054</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="17">
-        <v>1</v>
-      </c>
-      <c r="D26" s="33">
-        <f>D25</f>
-        <v>17.5</v>
-      </c>
-      <c r="E26" s="33">
-        <v>0.45</v>
-      </c>
-      <c r="F26" s="33">
-        <v>0.05</v>
-      </c>
-      <c r="G26" s="33">
-        <f t="shared" ref="G26:G31" si="0">PRODUCT(C26:F26)</f>
-        <v>0.39375000000000004</v>
-      </c>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
       <c r="H26" s="17"/>
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="36"/>
-      <c r="O26" s="36"/>
-      <c r="P26" s="36"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A27" s="16"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="17">
-        <v>1</v>
-      </c>
-      <c r="D27" s="33">
-        <f>D18</f>
-        <v>7.5</v>
-      </c>
-      <c r="E27" s="33">
-        <f>E18</f>
-        <v>1</v>
-      </c>
-      <c r="F27" s="33">
-        <v>0.05</v>
-      </c>
-      <c r="G27" s="33">
-        <f t="shared" si="0"/>
-        <v>0.375</v>
-      </c>
+    </row>
+    <row r="27" spans="1:16" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="16">
+        <v>3</v>
+      </c>
+      <c r="B27" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
       <c r="H27" s="17"/>
       <c r="I27" s="17"/>
       <c r="J27" s="17"/>
       <c r="K27" s="17"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="36"/>
-      <c r="O27" s="36"/>
-      <c r="P27" s="36"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
-      <c r="B28" s="32"/>
+      <c r="B28" s="32" t="str">
+        <f>B19</f>
+        <v>-for masonary wall</v>
+      </c>
       <c r="C28" s="17">
         <v>1</v>
       </c>
       <c r="D28" s="33">
-        <f>D27</f>
-        <v>7.5</v>
+        <f>D19</f>
+        <v>17.5</v>
       </c>
       <c r="E28" s="33">
-        <v>0.45</v>
+        <f>E19</f>
+        <v>1.5</v>
       </c>
       <c r="F28" s="33">
-        <v>0.05</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G28" s="33">
-        <f t="shared" si="0"/>
-        <v>0.16875000000000001</v>
+        <f>PRODUCT(C28:F28)</f>
+        <v>1.96875</v>
       </c>
       <c r="H28" s="17"/>
       <c r="I28" s="17"/>
       <c r="J28" s="17"/>
       <c r="K28" s="17"/>
-      <c r="M28" s="36"/>
-      <c r="N28" s="36"/>
-      <c r="O28" s="36"/>
-      <c r="P28" s="36"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M28" s="33">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="N28" s="33">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="O28" s="33"/>
+      <c r="P28" s="33">
+        <f>PI()*M28*SQRT(M28^2+N28^2)</f>
+        <v>160.09797821843054</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="16"/>
       <c r="B29" s="32"/>
       <c r="C29" s="17">
         <v>1</v>
       </c>
       <c r="D29" s="33">
-        <f>D19</f>
-        <v>10.5</v>
+        <f>D28</f>
+        <v>17.5</v>
       </c>
       <c r="E29" s="33">
-        <f>E19</f>
-        <v>1.2</v>
+        <v>0.45</v>
       </c>
       <c r="F29" s="33">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G29" s="33">
-        <f t="shared" si="0"/>
-        <v>1.26</v>
+        <f t="shared" ref="G29:G35" si="1">PRODUCT(C29:F29)</f>
+        <v>0.39375000000000004</v>
       </c>
       <c r="H29" s="17"/>
       <c r="I29" s="17"/>
@@ -1821,30 +1826,26 @@
       <c r="O29" s="36"/>
       <c r="P29" s="36"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="16"/>
-      <c r="B30" s="32" t="str">
-        <f>B20</f>
-        <v>-for footing</v>
-      </c>
-      <c r="C30" s="32">
-        <f t="shared" ref="C30:G31" si="1">C20</f>
-        <v>8</v>
-      </c>
-      <c r="D30" s="32">
+      <c r="B30" s="32"/>
+      <c r="C30" s="17">
+        <v>1</v>
+      </c>
+      <c r="D30" s="33">
+        <f>D20</f>
+        <v>7.9</v>
+      </c>
+      <c r="E30" s="33">
+        <f>E20</f>
+        <v>1</v>
+      </c>
+      <c r="F30" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G30" s="33">
         <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="E30" s="32">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="F30" s="32">
-        <v>0.05</v>
-      </c>
-      <c r="G30" s="33">
-        <f t="shared" si="0"/>
-        <v>8.1000000000000016E-2</v>
+        <v>0.59250000000000003</v>
       </c>
       <c r="H30" s="17"/>
       <c r="I30" s="17"/>
@@ -1855,25 +1856,25 @@
       <c r="O30" s="36"/>
       <c r="P30" s="36"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="16"/>
       <c r="B31" s="32"/>
-      <c r="C31" s="32">
-        <f>C30</f>
-        <v>8</v>
-      </c>
-      <c r="D31" s="32">
+      <c r="C31" s="17">
+        <v>1</v>
+      </c>
+      <c r="D31" s="33">
+        <f>D30</f>
+        <v>7.9</v>
+      </c>
+      <c r="E31" s="33">
         <v>0.45</v>
       </c>
-      <c r="E31" s="32">
-        <v>0.45</v>
-      </c>
-      <c r="F31" s="32">
-        <v>0.45</v>
+      <c r="F31" s="33">
+        <v>0.05</v>
       </c>
       <c r="G31" s="33">
-        <f t="shared" si="0"/>
-        <v>0.72900000000000009</v>
+        <f t="shared" si="1"/>
+        <v>0.17775000000000002</v>
       </c>
       <c r="H31" s="17"/>
       <c r="I31" s="17"/>
@@ -1884,107 +1885,158 @@
       <c r="O31" s="36"/>
       <c r="P31" s="36"/>
     </row>
-    <row r="32" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="6">
-        <f>SUM(G25:G31)</f>
-        <v>4.32</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I32" s="6">
-        <v>10964.46</v>
-      </c>
-      <c r="J32" s="18">
-        <f>G32*I32</f>
-        <v>47366.467199999999</v>
-      </c>
-      <c r="K32" s="5"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="16"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="17">
+        <v>1</v>
+      </c>
+      <c r="D32" s="33">
+        <f>D21</f>
+        <v>10.5</v>
+      </c>
+      <c r="E32" s="33">
+        <f>E21</f>
+        <v>1.2</v>
+      </c>
+      <c r="F32" s="33">
+        <v>0.1</v>
+      </c>
+      <c r="G32" s="33">
+        <f t="shared" si="1"/>
+        <v>1.26</v>
+      </c>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="M32" s="36"/>
+      <c r="N32" s="36"/>
+      <c r="O32" s="36"/>
+      <c r="P32" s="36"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="16"/>
-      <c r="B33" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
+      <c r="B33" s="32" t="str">
+        <f>B22</f>
+        <v>-for footing</v>
+      </c>
+      <c r="C33" s="32">
+        <f t="shared" ref="C33:E33" si="2">C22</f>
+        <v>8</v>
+      </c>
+      <c r="D33" s="32">
+        <f t="shared" si="2"/>
+        <v>0.45</v>
+      </c>
+      <c r="E33" s="32">
+        <f t="shared" si="2"/>
+        <v>0.45</v>
+      </c>
+      <c r="F33" s="32">
+        <v>0.05</v>
+      </c>
+      <c r="G33" s="33">
+        <f t="shared" si="1"/>
+        <v>8.1000000000000016E-2</v>
+      </c>
       <c r="H33" s="17"/>
       <c r="I33" s="17"/>
-      <c r="J33" s="18">
-        <f>0.13*G32*(53818.03)/15</f>
-        <v>2014.9470432000005</v>
-      </c>
+      <c r="J33" s="17"/>
       <c r="K33" s="17"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M33" s="36"/>
+      <c r="N33" s="36"/>
+      <c r="O33" s="36"/>
+      <c r="P33" s="36"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="16"/>
-      <c r="B34" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="32">
+        <f>C33</f>
+        <v>8</v>
+      </c>
+      <c r="D34" s="32">
+        <v>0.45</v>
+      </c>
+      <c r="E34" s="32">
+        <v>0.45</v>
+      </c>
+      <c r="F34" s="32">
+        <v>0.45</v>
+      </c>
+      <c r="G34" s="33">
+        <f t="shared" si="1"/>
+        <v>0.72900000000000009</v>
+      </c>
       <c r="H34" s="17"/>
       <c r="I34" s="17"/>
-      <c r="J34" s="18">
-        <f>0.13*G32*(21432.6)/15</f>
-        <v>802.43654400000014</v>
-      </c>
+      <c r="J34" s="17"/>
       <c r="K34" s="17"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M34" s="36"/>
+      <c r="N34" s="36"/>
+      <c r="O34" s="36"/>
+      <c r="P34" s="36"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="16"/>
       <c r="B35" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
+        <v>54</v>
+      </c>
+      <c r="C35" s="32">
+        <v>1</v>
+      </c>
+      <c r="D35" s="60">
+        <v>10</v>
+      </c>
+      <c r="E35" s="60">
+        <v>1.2</v>
+      </c>
+      <c r="F35" s="32">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G35" s="33">
+        <f t="shared" si="1"/>
+        <v>0.89999999999999991</v>
+      </c>
       <c r="H35" s="17"/>
       <c r="I35" s="17"/>
-      <c r="J35" s="18">
-        <f>0.13*G32*(25719.12+13573.98+4286.52)/15</f>
-        <v>1631.6209728000001</v>
-      </c>
+      <c r="J35" s="17"/>
       <c r="K35" s="17"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A36" s="16"/>
-      <c r="B36" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
+      <c r="M35" s="36"/>
+      <c r="N35" s="36"/>
+      <c r="O35" s="36"/>
+      <c r="P35" s="36"/>
+    </row>
+    <row r="36" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="6">
+        <f>SUM(G28:G35)</f>
+        <v>6.1027500000000003</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="6">
+        <v>10964.46</v>
+      </c>
       <c r="J36" s="18">
-        <f>0.13*G32*(6325.7)/15</f>
-        <v>236.83420800000005</v>
-      </c>
-      <c r="K36" s="17"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+        <f>G36*I36</f>
+        <v>66913.358265000003</v>
+      </c>
+      <c r="K36" s="5"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="16"/>
       <c r="B37" s="32" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
@@ -1994,14 +2046,16 @@
       <c r="H37" s="17"/>
       <c r="I37" s="17"/>
       <c r="J37" s="18">
-        <f>0.13*G32*(310)/5</f>
-        <v>34.819200000000009</v>
+        <f>0.13*G36*(53818.03)/15</f>
+        <v>2846.4625157150003</v>
       </c>
       <c r="K37" s="17"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="16"/>
-      <c r="B38" s="17"/>
+      <c r="B38" s="32" t="s">
+        <v>34</v>
+      </c>
       <c r="C38" s="17"/>
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
@@ -2009,15 +2063,16 @@
       <c r="G38" s="17"/>
       <c r="H38" s="17"/>
       <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
+      <c r="J38" s="18">
+        <f>0.13*G36*(21432.6)/15</f>
+        <v>1133.5809302999999</v>
+      </c>
       <c r="K38" s="17"/>
     </row>
-    <row r="39" spans="1:16" ht="109.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="16">
-        <v>4</v>
-      </c>
-      <c r="B39" s="35" t="s">
-        <v>37</v>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" s="16"/>
+      <c r="B39" s="32" t="s">
+        <v>35</v>
       </c>
       <c r="C39" s="17"/>
       <c r="D39" s="17"/>
@@ -2026,110 +2081,67 @@
       <c r="G39" s="17"/>
       <c r="H39" s="17"/>
       <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
+      <c r="J39" s="18">
+        <f>0.13*G36*(25719.12+13573.98+4286.52)/15</f>
+        <v>2304.9478916099997</v>
+      </c>
       <c r="K39" s="17"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="16"/>
-      <c r="B40" s="32" t="str">
-        <f>B25</f>
-        <v>-for masonary wall</v>
-      </c>
-      <c r="C40" s="17">
-        <v>1</v>
-      </c>
-      <c r="D40" s="33">
-        <f>D10</f>
-        <v>17.5</v>
-      </c>
-      <c r="E40" s="33">
-        <f>((F40/2)+0.45)/2</f>
-        <v>0.97499999999999998</v>
-      </c>
-      <c r="F40" s="33">
-        <v>3</v>
-      </c>
-      <c r="G40" s="33">
-        <f>PRODUCT(C40:F40)</f>
-        <v>51.1875</v>
-      </c>
+      <c r="B40" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
       <c r="H40" s="17"/>
       <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
+      <c r="J40" s="18">
+        <f>0.13*G36*(6325.7)/15</f>
+        <v>334.56943585000005</v>
+      </c>
       <c r="K40" s="17"/>
-      <c r="M40" s="33">
-        <f>7</f>
-        <v>7</v>
-      </c>
-      <c r="N40" s="33">
-        <f>2</f>
-        <v>2</v>
-      </c>
-      <c r="O40" s="33"/>
-      <c r="P40" s="33">
-        <f>PI()*M40*SQRT(M40^2+N40^2)</f>
-        <v>160.09797821843054</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="16"/>
-      <c r="B41" s="32"/>
-      <c r="C41" s="17">
-        <v>1</v>
-      </c>
-      <c r="D41" s="33">
-        <f>D11</f>
-        <v>7.5</v>
-      </c>
-      <c r="E41" s="33">
-        <f>((F41/2)+0.45)/2</f>
-        <v>0.72499999999999998</v>
-      </c>
-      <c r="F41" s="33">
-        <v>2</v>
-      </c>
-      <c r="G41" s="33">
-        <f>PRODUCT(C41:F41)</f>
-        <v>10.875</v>
-      </c>
+      <c r="B41" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
       <c r="H41" s="17"/>
       <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
+      <c r="J41" s="18">
+        <f>0.13*G36*(310)/5</f>
+        <v>49.188165000000005</v>
+      </c>
       <c r="K41" s="17"/>
-      <c r="M41" s="50"/>
-      <c r="N41" s="50"/>
-      <c r="O41" s="50"/>
-      <c r="P41" s="50"/>
-    </row>
-    <row r="42" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="2"/>
-      <c r="B42" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="6">
-        <f>SUM(G40:G41)</f>
-        <v>62.0625</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I42" s="6">
-        <v>8987.83</v>
-      </c>
-      <c r="J42" s="18">
-        <f>G42*I42</f>
-        <v>557807.19937499997</v>
-      </c>
-      <c r="K42" s="5"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A43" s="16"/>
-      <c r="B43" s="32" t="s">
-        <v>33</v>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" s="16"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+    </row>
+    <row r="43" spans="1:16" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A43" s="16">
+        <v>4</v>
+      </c>
+      <c r="B43" s="35" t="s">
+        <v>37</v>
       </c>
       <c r="C43" s="17"/>
       <c r="D43" s="17"/>
@@ -2138,69 +2150,111 @@
       <c r="G43" s="17"/>
       <c r="H43" s="17"/>
       <c r="I43" s="17"/>
-      <c r="J43" s="18">
-        <f>0.13*G42*(5863.95)/5</f>
-        <v>9462.2163187500009</v>
-      </c>
+      <c r="J43" s="17"/>
       <c r="K43" s="17"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="16"/>
-      <c r="B44" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
+      <c r="B44" s="32" t="str">
+        <f>B28</f>
+        <v>-for masonary wall</v>
+      </c>
+      <c r="C44" s="17">
+        <v>1</v>
+      </c>
+      <c r="D44" s="33">
+        <f>D10</f>
+        <v>17.5</v>
+      </c>
+      <c r="E44" s="33">
+        <f>((F44/2)+0.45)/2</f>
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="F44" s="33">
+        <v>3</v>
+      </c>
+      <c r="G44" s="33">
+        <f>PRODUCT(C44:F44)</f>
+        <v>51.1875</v>
+      </c>
       <c r="H44" s="17"/>
       <c r="I44" s="17"/>
-      <c r="J44" s="18">
-        <f>0.13*G42*(6604.416)/5</f>
-        <v>10657.050768000001</v>
-      </c>
+      <c r="J44" s="17"/>
       <c r="K44" s="17"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M44" s="33">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="N44" s="33">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="O44" s="33"/>
+      <c r="P44" s="33">
+        <f>PI()*M44*SQRT(M44^2+N44^2)</f>
+        <v>160.09797821843054</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="16"/>
-      <c r="B45" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
+      <c r="B45" s="32"/>
+      <c r="C45" s="17">
+        <v>1</v>
+      </c>
+      <c r="D45" s="33">
+        <f>D11</f>
+        <v>7.9</v>
+      </c>
+      <c r="E45" s="33">
+        <f>((F45/2)+0.45)/2</f>
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="F45" s="33">
+        <v>2</v>
+      </c>
+      <c r="G45" s="33">
+        <f>PRODUCT(C45:F45)</f>
+        <v>11.455</v>
+      </c>
       <c r="H45" s="17"/>
       <c r="I45" s="17"/>
-      <c r="J45" s="18">
-        <f>0.13*G42*(14808.78)/5</f>
-        <v>23895.817627500001</v>
-      </c>
+      <c r="J45" s="17"/>
       <c r="K45" s="17"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A46" s="16"/>
-      <c r="B46" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17"/>
-      <c r="I46" s="17"/>
+      <c r="M45" s="36"/>
+      <c r="N45" s="36"/>
+      <c r="O45" s="36"/>
+      <c r="P45" s="36"/>
+    </row>
+    <row r="46" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2"/>
+      <c r="B46" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="6">
+        <f>SUM(G44:G45)</f>
+        <v>62.642499999999998</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I46" s="6">
+        <v>8987.83</v>
+      </c>
       <c r="J46" s="18">
-        <f>0.13*G42*(310)/5</f>
-        <v>500.22375</v>
-      </c>
-      <c r="K46" s="17"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+        <f>G46*I46</f>
+        <v>563020.14077499998</v>
+      </c>
+      <c r="K46" s="5"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="16"/>
-      <c r="B47" s="17"/>
+      <c r="B47" s="32" t="s">
+        <v>33</v>
+      </c>
       <c r="C47" s="17"/>
       <c r="D47" s="17"/>
       <c r="E47" s="17"/>
@@ -2208,357 +2262,445 @@
       <c r="G47" s="17"/>
       <c r="H47" s="17"/>
       <c r="I47" s="17"/>
-      <c r="J47" s="17"/>
+      <c r="J47" s="18">
+        <f>0.13*G46*(5863.95)/5</f>
+        <v>9550.644684750001</v>
+      </c>
       <c r="K47" s="17"/>
     </row>
-    <row r="48" spans="1:16" s="59" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="51">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" s="16"/>
+      <c r="B48" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="18">
+        <f>0.13*G46*(6604.416)/5</f>
+        <v>10756.64536128</v>
+      </c>
+      <c r="K48" s="17"/>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A49" s="16"/>
+      <c r="B49" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="18">
+        <f>0.13*G46*(14808.78)/5</f>
+        <v>24119.134029900004</v>
+      </c>
+      <c r="K49" s="17"/>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A50" s="16"/>
+      <c r="B50" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="18">
+        <f>0.13*G46*(310)/5</f>
+        <v>504.89855</v>
+      </c>
+      <c r="K50" s="17"/>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A51" s="16"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+    </row>
+    <row r="52" spans="1:19" s="41" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
         <v>5</v>
       </c>
-      <c r="B48" s="52" t="s">
+      <c r="B52" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="53" t="s">
+      <c r="C52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D48" s="54" t="s">
+      <c r="D52" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="E48" s="55" t="s">
+      <c r="E52" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="F48" s="55" t="s">
+      <c r="F52" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="G48" s="55"/>
-      <c r="H48" s="56"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="57"/>
-      <c r="K48" s="58"/>
-    </row>
-    <row r="49" spans="1:19" s="59" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="60"/>
-      <c r="B49" s="61" t="s">
+      <c r="G52" s="39"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="40"/>
+      <c r="K52" s="5"/>
+    </row>
+    <row r="53" spans="1:19" s="41" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="42"/>
+      <c r="B53" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="62">
+      <c r="C53" s="44">
         <f>4*2</f>
         <v>8</v>
       </c>
-      <c r="D49" s="63">
+      <c r="D53" s="45">
+        <v>1.8</v>
+      </c>
+      <c r="E53" s="45">
+        <v>3.97</v>
+      </c>
+      <c r="F53" s="45">
+        <f>PRODUCT(C53:E53)</f>
+        <v>57.168000000000006</v>
+      </c>
+      <c r="G53" s="9">
+        <f>F53</f>
+        <v>57.168000000000006</v>
+      </c>
+      <c r="H53" s="40"/>
+      <c r="I53" s="40"/>
+      <c r="J53" s="40"/>
+      <c r="K53" s="46"/>
+    </row>
+    <row r="54" spans="1:19" s="41" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="42"/>
+      <c r="B54" s="43"/>
+      <c r="C54" s="44">
+        <v>4</v>
+      </c>
+      <c r="D54" s="45">
         <v>1.2</v>
       </c>
-      <c r="E49" s="63">
+      <c r="E54" s="45">
         <v>3.97</v>
       </c>
-      <c r="F49" s="63">
-        <f>PRODUCT(C49:E49)</f>
-        <v>38.112000000000002</v>
-      </c>
-      <c r="G49" s="9">
-        <f>F49</f>
-        <v>38.112000000000002</v>
-      </c>
-      <c r="H49" s="57"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="57"/>
-      <c r="K49" s="64"/>
-      <c r="M49" s="65"/>
-    </row>
-    <row r="50" spans="1:19" s="59" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="60"/>
-      <c r="B50" s="61"/>
-      <c r="C50" s="62">
-        <v>4</v>
-      </c>
-      <c r="D50" s="63">
-        <v>1.2</v>
-      </c>
-      <c r="E50" s="63">
+      <c r="F54" s="45">
+        <f>PRODUCT(C54:E54)</f>
+        <v>19.056000000000001</v>
+      </c>
+      <c r="G54" s="9">
+        <f>F54</f>
+        <v>19.056000000000001</v>
+      </c>
+      <c r="H54" s="40"/>
+      <c r="I54" s="40"/>
+      <c r="J54" s="40"/>
+      <c r="K54" s="46"/>
+    </row>
+    <row r="55" spans="1:19" s="41" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="42"/>
+      <c r="B55" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C55" s="44">
+        <f>4*2</f>
+        <v>8</v>
+      </c>
+      <c r="D55" s="45">
+        <v>0.75</v>
+      </c>
+      <c r="E55" s="45">
         <v>3.97</v>
       </c>
-      <c r="F50" s="63">
-        <f>PRODUCT(C50:E50)</f>
-        <v>19.056000000000001</v>
-      </c>
-      <c r="G50" s="9">
-        <f>F50</f>
-        <v>19.056000000000001</v>
-      </c>
-      <c r="H50" s="57"/>
-      <c r="I50" s="57"/>
-      <c r="J50" s="57"/>
-      <c r="K50" s="64"/>
-      <c r="M50" s="65"/>
-    </row>
-    <row r="51" spans="1:19" s="59" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="51"/>
-      <c r="B51" s="61" t="s">
+      <c r="F55" s="45">
+        <f>PRODUCT(C55:E55)</f>
+        <v>23.82</v>
+      </c>
+      <c r="G55" s="9">
+        <f>F55</f>
+        <v>23.82</v>
+      </c>
+      <c r="H55" s="40"/>
+      <c r="I55" s="40"/>
+      <c r="J55" s="40"/>
+      <c r="K55" s="46"/>
+    </row>
+    <row r="56" spans="1:19" s="41" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2"/>
+      <c r="B56" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="C51" s="53"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="58"/>
-      <c r="F51" s="58"/>
-      <c r="G51" s="57">
-        <f>SUM(G49:G50)</f>
-        <v>57.168000000000006</v>
-      </c>
-      <c r="H51" s="56" t="s">
-        <v>50</v>
-      </c>
-      <c r="I51" s="6">
-        <v>182.51</v>
-      </c>
-      <c r="J51" s="57">
-        <f>G51*I51</f>
-        <v>10433.731680000001</v>
-      </c>
-      <c r="K51" s="58"/>
-    </row>
-    <row r="52" spans="1:19" s="59" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="51"/>
-      <c r="B52" s="61" t="s">
-        <v>51</v>
-      </c>
-      <c r="C52" s="53"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="58"/>
-      <c r="F52" s="58"/>
-      <c r="G52" s="57"/>
-      <c r="H52" s="56"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="57">
-        <f>0.13*G51*(1871.42/18.94)</f>
-        <v>734.3238655121437</v>
-      </c>
-      <c r="K52" s="58"/>
-    </row>
-    <row r="53" spans="1:19" s="59" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="51"/>
-      <c r="B53" s="61"/>
-      <c r="C53" s="53"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="58"/>
-      <c r="F53" s="58"/>
-      <c r="G53" s="57"/>
-      <c r="H53" s="56"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="57"/>
-      <c r="K53" s="58"/>
-    </row>
-    <row r="54" spans="1:19" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="2">
-        <v>6</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C54" s="3">
-        <v>1</v>
-      </c>
-      <c r="D54" s="4"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="7">
-        <f t="shared" ref="G54" si="2">PRODUCT(C54:F54)</f>
-        <v>1</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="I54" s="6">
-        <v>20000</v>
-      </c>
-      <c r="J54" s="7">
-        <f>G54*I54</f>
-        <v>20000</v>
-      </c>
-      <c r="K54" s="5"/>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A55" s="2"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="18"/>
-      <c r="K55" s="5"/>
-    </row>
-    <row r="56" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="2">
-        <v>7</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C56" s="3">
-        <v>1</v>
-      </c>
+      <c r="C56" s="3"/>
       <c r="D56" s="4"/>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
-      <c r="G56" s="7">
-        <f t="shared" ref="G56" si="3">PRODUCT(C56:F56)</f>
-        <v>1</v>
+      <c r="G56" s="40">
+        <f>SUM(G53:G55)</f>
+        <v>100.04400000000001</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I56" s="6">
-        <v>500</v>
-      </c>
-      <c r="J56" s="7">
+        <v>182.51</v>
+      </c>
+      <c r="J56" s="40">
         <f>G56*I56</f>
-        <v>500</v>
+        <v>18259.030440000002</v>
       </c>
       <c r="K56" s="5"/>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" s="41" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
-      <c r="B57" s="8"/>
+      <c r="B57" s="43" t="s">
+        <v>51</v>
+      </c>
       <c r="C57" s="3"/>
       <c r="D57" s="4"/>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
-      <c r="G57" s="6"/>
+      <c r="G57" s="40"/>
       <c r="H57" s="7"/>
       <c r="I57" s="6"/>
-      <c r="J57" s="18"/>
+      <c r="J57" s="40">
+        <f>0.13*G56*(1871.42/18.94)</f>
+        <v>1285.0667646462516</v>
+      </c>
       <c r="K57" s="5"/>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A58" s="21"/>
-      <c r="B58" s="22" t="s">
+    <row r="58" spans="1:19" s="41" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2"/>
+      <c r="B58" s="43"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="40"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="40"/>
+      <c r="K58" s="5"/>
+    </row>
+    <row r="59" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>6</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C59" s="3">
+        <v>1</v>
+      </c>
+      <c r="D59" s="4"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="7">
+        <f t="shared" ref="G59" si="3">PRODUCT(C59:F59)</f>
+        <v>1</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I59" s="6">
+        <v>30000</v>
+      </c>
+      <c r="J59" s="7">
+        <f>G59*I59</f>
+        <v>30000</v>
+      </c>
+      <c r="K59" s="5"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="2"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="5"/>
+    </row>
+    <row r="61" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>7</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C61" s="3">
+        <v>1</v>
+      </c>
+      <c r="D61" s="4"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="7">
+        <f t="shared" ref="G61" si="4">PRODUCT(C61:F61)</f>
+        <v>1</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I61" s="6">
+        <v>1000</v>
+      </c>
+      <c r="J61" s="7">
+        <f>G61*I61</f>
+        <v>1000</v>
+      </c>
+      <c r="K61" s="5"/>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A62" s="2"/>
+      <c r="B62" s="8"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="5"/>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A63" s="21"/>
+      <c r="B63" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C58" s="23"/>
-      <c r="D58" s="24"/>
-      <c r="E58" s="24"/>
-      <c r="F58" s="24"/>
-      <c r="G58" s="18"/>
-      <c r="H58" s="18"/>
-      <c r="I58" s="18"/>
-      <c r="J58" s="18">
-        <f>SUM(J9:J56)</f>
-        <v>727594.42471356213</v>
-      </c>
-      <c r="K58" s="25"/>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="M59" s="20"/>
-      <c r="N59" s="20"/>
-      <c r="O59" s="20"/>
-      <c r="P59" s="20"/>
-      <c r="Q59" s="20"/>
-      <c r="R59" s="20"/>
-      <c r="S59" s="20"/>
-    </row>
-    <row r="60" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="26"/>
-      <c r="B60" s="27" t="s">
+      <c r="C63" s="23"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="18"/>
+      <c r="H63" s="18"/>
+      <c r="I63" s="18"/>
+      <c r="J63" s="18">
+        <f>SUM(J9:J61)</f>
+        <v>782852.69511785114</v>
+      </c>
+      <c r="K63" s="25"/>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="M64" s="20"/>
+      <c r="N64" s="20"/>
+      <c r="O64" s="20"/>
+      <c r="P64" s="20"/>
+      <c r="Q64" s="20"/>
+      <c r="R64" s="20"/>
+      <c r="S64" s="20"/>
+    </row>
+    <row r="65" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="26"/>
+      <c r="B65" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C60" s="43">
-        <f>J58</f>
-        <v>727594.42471356213</v>
-      </c>
-      <c r="D60" s="44"/>
-      <c r="E60" s="9">
+      <c r="C65" s="47">
+        <f>J63</f>
+        <v>782852.69511785114</v>
+      </c>
+      <c r="D65" s="48"/>
+      <c r="E65" s="9">
         <v>100</v>
       </c>
-      <c r="F60" s="26"/>
-      <c r="G60" s="28"/>
-      <c r="H60" s="26"/>
-      <c r="I60" s="29"/>
-      <c r="J60" s="30"/>
-      <c r="K60" s="31"/>
-      <c r="M60" s="19"/>
-      <c r="N60" s="19"/>
-      <c r="O60" s="19"/>
-      <c r="P60" s="19"/>
-      <c r="Q60" s="19"/>
-      <c r="R60" s="19"/>
-      <c r="S60" s="19"/>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B61" s="27" t="s">
+      <c r="F65" s="26"/>
+      <c r="G65" s="28"/>
+      <c r="H65" s="26"/>
+      <c r="I65" s="29"/>
+      <c r="J65" s="30"/>
+      <c r="K65" s="31"/>
+      <c r="M65" s="19"/>
+      <c r="N65" s="19"/>
+      <c r="O65" s="19"/>
+      <c r="P65" s="19"/>
+      <c r="Q65" s="19"/>
+      <c r="R65" s="19"/>
+      <c r="S65" s="19"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B66" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C61" s="47">
-        <v>650000</v>
-      </c>
-      <c r="D61" s="48"/>
-      <c r="E61" s="9"/>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B62" s="27" t="s">
+      <c r="C66" s="51">
+        <v>700000</v>
+      </c>
+      <c r="D66" s="52"/>
+      <c r="E66" s="9"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B67" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C62" s="47">
-        <f>C61-C64-C65</f>
-        <v>617500</v>
-      </c>
-      <c r="D62" s="48"/>
-      <c r="E62" s="9">
-        <f>C62/C60*100</f>
-        <v>84.868709685769801</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B63" s="27" t="s">
+      <c r="C67" s="51">
+        <f>C66-C69-C70</f>
+        <v>665000</v>
+      </c>
+      <c r="D67" s="52"/>
+      <c r="E67" s="9">
+        <f>C67/C65*100</f>
+        <v>84.94573808676617</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B68" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C63" s="49">
-        <f>C60-C62</f>
-        <v>110094.42471356213</v>
-      </c>
-      <c r="D63" s="49"/>
-      <c r="E63" s="9">
-        <f>100-E62</f>
-        <v>15.131290314230199</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B64" s="27" t="s">
+      <c r="C68" s="53">
+        <f>C65-C67</f>
+        <v>117852.69511785114</v>
+      </c>
+      <c r="D68" s="53"/>
+      <c r="E68" s="9">
+        <f>100-E67</f>
+        <v>15.05426191323383</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B69" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C64" s="43">
-        <f>C61*0.03</f>
-        <v>19500</v>
-      </c>
-      <c r="D64" s="44"/>
-      <c r="E64" s="9">
+      <c r="C69" s="47">
+        <f>C66*0.03</f>
+        <v>21000</v>
+      </c>
+      <c r="D69" s="48"/>
+      <c r="E69" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B65" s="27" t="s">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B70" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="C65" s="43">
-        <f>C61*0.02</f>
-        <v>13000</v>
-      </c>
-      <c r="D65" s="44"/>
-      <c r="E65" s="9">
+      <c r="C70" s="47">
+        <f>C66*0.02</f>
+        <v>14000</v>
+      </c>
+      <c r="D70" s="48"/>
+      <c r="E70" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
@@ -2566,14 +2708,19 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C68:D68"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
   </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="38" max="10" man="1"/>
-  </rowBreaks>
 </worksheet>
 </file>